--- a/calibration_plots/plot_data_vertebral_rf.xlsx
+++ b/calibration_plots/plot_data_vertebral_rf.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -368,66 +368,50 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0.526</v>
+        <v>0.543433962264151</v>
       </c>
       <c r="B2">
-        <v>0.6</v>
+        <v>0.5849056603773585</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.6313684210526316</v>
+        <v>0.6835384615384615</v>
       </c>
       <c r="B3">
-        <v>0.6052631578947368</v>
+        <v>0.6346153846153846</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.7358974358974359</v>
+        <v>0.8348</v>
       </c>
       <c r="B4">
-        <v>0.717948717948718</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.851421052631579</v>
+        <v>0.9287547169811321</v>
       </c>
       <c r="B5">
-        <v>0.9473684210526315</v>
+        <v>0.9433962264150944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.9218000000000001</v>
+        <v>0.9777090909090909</v>
       </c>
       <c r="B6">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.9621621621621621</v>
+        <v>0.9968510638297873</v>
       </c>
       <c r="B7">
-        <v>0.972972972972973</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>0.9870697674418605</v>
-      </c>
-      <c r="B8">
-        <v>0.9767441860465116</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>0.9981142857142857</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
+        <v>0.9787234042553191</v>
       </c>
     </row>
   </sheetData>
